--- a/reports/powerbi/powerbi_dashboard_dataset.xlsx
+++ b/reports/powerbi/powerbi_dashboard_dataset.xlsx
@@ -13,10 +13,11 @@
     <sheet name="user_type" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="repeat_rate" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="rfm_summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="channel_metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="region_metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="country_metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="country_gap" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="high_value_profile" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="data_quality" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="channel_limitation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="data_quality" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,229 +456,248 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77351.28</v>
+        <v>570422.73</v>
       </c>
       <c r="C2" t="n">
-        <v>213</v>
+        <v>1400</v>
       </c>
       <c r="D2" t="n">
-        <v>204</v>
+        <v>885</v>
       </c>
       <c r="E2" t="n">
-        <v>363.15</v>
+        <v>407.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57719.31</v>
+        <v>568101.3100000001</v>
       </c>
       <c r="C3" t="n">
-        <v>163</v>
+        <v>987</v>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>741</v>
       </c>
       <c r="E3" t="n">
-        <v>354.11</v>
+        <v>575.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84363.44</v>
+        <v>446084.92</v>
       </c>
       <c r="C4" t="n">
-        <v>263</v>
+        <v>997</v>
       </c>
       <c r="D4" t="n">
-        <v>242</v>
+        <v>758</v>
       </c>
       <c r="E4" t="n">
-        <v>320.77</v>
+        <v>447.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84127.03</v>
+        <v>594081.76</v>
       </c>
       <c r="C5" t="n">
-        <v>247</v>
+        <v>1321</v>
       </c>
       <c r="D5" t="n">
-        <v>226</v>
+        <v>974</v>
       </c>
       <c r="E5" t="n">
-        <v>340.6</v>
+        <v>449.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>103376.1</v>
+        <v>468374.33</v>
       </c>
       <c r="C6" t="n">
-        <v>281</v>
+        <v>1149</v>
       </c>
       <c r="D6" t="n">
-        <v>253</v>
+        <v>856</v>
       </c>
       <c r="E6" t="n">
-        <v>367.89</v>
+        <v>407.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87621.78</v>
+        <v>677355.15</v>
       </c>
       <c r="C7" t="n">
-        <v>291</v>
+        <v>1555</v>
       </c>
       <c r="D7" t="n">
-        <v>268</v>
+        <v>1056</v>
       </c>
       <c r="E7" t="n">
-        <v>301.11</v>
+        <v>435.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83511.94</v>
+        <v>660046.05</v>
       </c>
       <c r="C8" t="n">
-        <v>239</v>
+        <v>1393</v>
       </c>
       <c r="D8" t="n">
-        <v>226</v>
+        <v>991</v>
       </c>
       <c r="E8" t="n">
-        <v>349.42</v>
+        <v>473.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78261.07000000001</v>
+        <v>598962.9</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>1331</v>
       </c>
       <c r="D9" t="n">
-        <v>241</v>
+        <v>949</v>
       </c>
       <c r="E9" t="n">
-        <v>303.34</v>
+        <v>450.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90459.37</v>
+        <v>644051.04</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>1280</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>935</v>
       </c>
       <c r="E10" t="n">
-        <v>330.14</v>
+        <v>503.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>85971.56</v>
+        <v>950690.2</v>
       </c>
       <c r="C11" t="n">
-        <v>274</v>
+        <v>1755</v>
       </c>
       <c r="D11" t="n">
-        <v>250</v>
+        <v>1266</v>
       </c>
       <c r="E11" t="n">
-        <v>313.76</v>
+        <v>541.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>114518.06</v>
+        <v>1035642.45</v>
       </c>
       <c r="C12" t="n">
-        <v>391</v>
+        <v>1929</v>
       </c>
       <c r="D12" t="n">
-        <v>337</v>
+        <v>1364</v>
       </c>
       <c r="E12" t="n">
-        <v>292.89</v>
+        <v>536.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101424.96</v>
+        <v>1156205.61</v>
       </c>
       <c r="C13" t="n">
-        <v>342</v>
+        <v>2657</v>
       </c>
       <c r="D13" t="n">
-        <v>301</v>
+        <v>1664</v>
       </c>
       <c r="E13" t="n">
-        <v>296.56</v>
+        <v>435.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>517190.44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>778</v>
+      </c>
+      <c r="D14" t="n">
+        <v>615</v>
+      </c>
+      <c r="E14" t="n">
+        <v>664.77</v>
       </c>
     </row>
   </sheetData>
@@ -691,51 +711,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>渠道分析限制</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UCI Online Retail 原始数据不包含广告渠道、流量来源或转化漏斗字段，因此本项目不伪造渠道分析，改用真实国家/地区字段做区域表现分析。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>dataset_url</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>raw_rows</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cancel_rows</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>missing_customer_rows</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>negative_or_zero_quantity_rows</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>non_positive_price_rows</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>rows_after_required_drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>duplicate_orders_removed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>clean_rows</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>paid_clean_rows</t>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>required_rows_removed</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>duplicate_rows_removed</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>clean_rows_before_business_filter</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>valid_purchase_rows</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>valid_orders</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>valid_users</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>date_min</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>date_max</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3645</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3583</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UCI Online Retail</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://archive.ics.uci.edu/dataset/352/online+retail</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>541909</v>
       </c>
       <c r="D2" t="n">
-        <v>3540</v>
+        <v>9288</v>
       </c>
       <c r="E2" t="n">
-        <v>3236</v>
+        <v>135080</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10624</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2517</v>
+      </c>
+      <c r="H2" t="n">
+        <v>406829</v>
+      </c>
+      <c r="I2" t="n">
+        <v>135080</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5225</v>
+      </c>
+      <c r="K2" t="n">
+        <v>401604</v>
+      </c>
+      <c r="L2" t="n">
+        <v>392692</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18532</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4338</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2010-12-01 08:26:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2011-12-09 12:50:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -749,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,96 +936,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>数码配件</t>
+          <t>其他商品</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>291480.67</v>
+        <v>2614170.33</v>
       </c>
       <c r="C2" t="n">
-        <v>667</v>
+        <v>15557</v>
       </c>
       <c r="D2" t="n">
-        <v>519</v>
+        <v>4049</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2779</v>
+        <v>0.2941</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>家居生活</t>
+          <t>礼品套装</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>288345.77</v>
+        <v>2356228.6</v>
       </c>
       <c r="C3" t="n">
-        <v>584</v>
+        <v>14586</v>
       </c>
       <c r="D3" t="n">
-        <v>486</v>
+        <v>3898</v>
       </c>
       <c r="E3" t="n">
-        <v>0.275</v>
+        <v>0.2651</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>服饰鞋包</t>
+          <t>家居装饰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>264528.8</v>
+        <v>1786295.2</v>
       </c>
       <c r="C4" t="n">
-        <v>648</v>
+        <v>13892</v>
       </c>
       <c r="D4" t="n">
-        <v>518</v>
+        <v>3846</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2522</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>美妆个护</t>
+          <t>厨房餐具</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>130981.54</v>
+        <v>1315517.29</v>
       </c>
       <c r="C5" t="n">
-        <v>701</v>
+        <v>12455</v>
       </c>
       <c r="D5" t="n">
-        <v>547</v>
+        <v>3588</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1249</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>收纳用品</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73369.12</v>
+        <v>408962.18</v>
       </c>
       <c r="C6" t="n">
-        <v>636</v>
+        <v>5768</v>
       </c>
       <c r="D6" t="n">
-        <v>520</v>
+        <v>2161</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>节日季节</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>255607.74</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5599</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0288</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>儿童用品</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>120906.02</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3598</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1731</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0136</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>服饰配件</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>29521.53</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D9" t="n">
+        <v>773</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0033</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +1096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,261 +1134,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>人体工学椅</t>
+          <t>PAPER CRAFT , LITTLE BIRDIE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>家居生活</t>
+          <t>其他商品</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>216876.61</v>
+        <v>168469.6</v>
       </c>
       <c r="E2" t="n">
-        <v>264</v>
+        <v>80995</v>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智能手表</t>
+          <t>REGENCY CAKESTAND 3 TIER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>数码配件</t>
+          <t>厨房餐具</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>154523.33</v>
+        <v>142264.75</v>
       </c>
       <c r="E3" t="n">
-        <v>321</v>
+        <v>12374</v>
       </c>
       <c r="F3" t="n">
-        <v>235</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>85123A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>跑步运动鞋</t>
+          <t>WHITE HANGING HEART T-LIGHT HOLDER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>服饰鞋包</t>
+          <t>家居装饰</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>115240.01</v>
+        <v>100392.1</v>
       </c>
       <c r="E4" t="n">
-        <v>358</v>
+        <v>36706</v>
       </c>
       <c r="F4" t="n">
-        <v>229</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>85099B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>轻薄羽绒服</t>
+          <t>JUMBO BAG RED RETROSPOT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>服饰鞋包</t>
+          <t>礼品套装</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>105060.94</v>
+        <v>85040.53999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>286</v>
+        <v>46078</v>
       </c>
       <c r="F5" t="n">
-        <v>206</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>精华液礼盒</t>
+          <t>MEDIUM CERAMIC TOP STORAGE JAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>美妆个护</t>
+          <t>收纳用品</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>84069.5</v>
+        <v>81416.73</v>
       </c>
       <c r="E6" t="n">
-        <v>343</v>
+        <v>77916</v>
       </c>
       <c r="F6" t="n">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>POSTAGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>数码配件</t>
+          <t>礼品套装</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77440.41</v>
+        <v>77803.96000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>283</v>
+        <v>3120</v>
       </c>
       <c r="F7" t="n">
-        <v>204</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>47566</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>无线蓝牙耳机</t>
+          <t>PARTY BUNTING</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>数码配件</t>
+          <t>节日季节</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59516.93</v>
+        <v>68785.23</v>
       </c>
       <c r="E8" t="n">
-        <v>348</v>
+        <v>15279</v>
       </c>
       <c r="F8" t="n">
-        <v>228</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>84879</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>香薰加湿器</t>
+          <t>ASSORTED COLOUR BIRD ORNAMENT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>家居生活</t>
+          <t>其他商品</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44787.84</v>
+        <v>56413.03</v>
       </c>
       <c r="E9" t="n">
-        <v>246</v>
+        <v>35263</v>
       </c>
       <c r="F9" t="n">
-        <v>187</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>通勤帆布包</t>
+          <t>Manual</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>服饰鞋包</t>
+          <t>其他商品</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44227.85</v>
+        <v>53419.93</v>
       </c>
       <c r="E10" t="n">
-        <v>307</v>
+        <v>6933</v>
       </c>
       <c r="F10" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>RABBIT NIGHT LIGHT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居装饰</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33671.02</v>
+        <v>51251.24</v>
       </c>
       <c r="E11" t="n">
-        <v>286</v>
+        <v>27153</v>
       </c>
       <c r="F11" t="n">
-        <v>195</v>
+        <v>801</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>79321</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CHILLI LIGHTS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>家居装饰</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>46265.11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9646</v>
+      </c>
+      <c r="F12" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>22086</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PAPER CHAIN KIT 50'S CHRISTMAS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>节日季节</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>42584.13</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15591</v>
+      </c>
+      <c r="F13" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22502</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PICNIC BASKET WICKER 60 PIECES</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>收纳用品</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>39619.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>61</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21137</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BLACK RECORD COVER FRAME</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>家居装饰</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>39045.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11401</v>
+      </c>
+      <c r="F15" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>22386</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JUMBO BAG PINK POLKADOT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>礼品套装</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>37254.36</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -1191,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1219,7 +1560,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1228,16 +1569,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>204</v>
+        <v>885</v>
       </c>
       <c r="D2" t="n">
-        <v>77351.28</v>
+        <v>570422.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1246,16 +1587,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>133</v>
+        <v>417</v>
       </c>
       <c r="D3" t="n">
-        <v>51950.44</v>
+        <v>292366.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1264,16 +1605,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="D4" t="n">
-        <v>5768.87</v>
+        <v>275734.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1282,16 +1623,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>179</v>
+        <v>380</v>
       </c>
       <c r="D5" t="n">
-        <v>65774.44</v>
+        <v>157700.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1300,16 +1641,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>378</v>
       </c>
       <c r="D6" t="n">
-        <v>18589</v>
+        <v>288384.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1318,16 +1659,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>139</v>
+        <v>452</v>
       </c>
       <c r="D7" t="n">
-        <v>51651.79</v>
+        <v>199619.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1336,16 +1677,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>87</v>
+        <v>522</v>
       </c>
       <c r="D8" t="n">
-        <v>32475.24</v>
+        <v>394462.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1354,16 +1695,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>131</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>55888.26</v>
+        <v>121809.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1372,16 +1713,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>556</v>
       </c>
       <c r="D10" t="n">
-        <v>47487.84</v>
+        <v>346565.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1390,16 +1731,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>284</v>
       </c>
       <c r="D11" t="n">
-        <v>36240.48</v>
+        <v>123739.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1408,16 +1749,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>772</v>
       </c>
       <c r="D12" t="n">
-        <v>51381.3</v>
+        <v>553615.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1426,16 +1767,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="D13" t="n">
-        <v>31976.82</v>
+        <v>135414.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1444,16 +1785,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>137</v>
+        <v>749</v>
       </c>
       <c r="D14" t="n">
-        <v>51535.12</v>
+        <v>524631.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1462,16 +1803,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>188</v>
       </c>
       <c r="D15" t="n">
-        <v>27303.7</v>
+        <v>73860.39999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1480,16 +1821,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>163</v>
+        <v>761</v>
       </c>
       <c r="D16" t="n">
-        <v>50957.37</v>
+        <v>525102.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1498,16 +1839,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="D17" t="n">
-        <v>18850.6</v>
+        <v>79601.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1516,16 +1857,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>205</v>
+        <v>766</v>
       </c>
       <c r="D18" t="n">
-        <v>71608.77</v>
+        <v>564449.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1534,16 +1875,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>299</v>
       </c>
       <c r="D19" t="n">
-        <v>19720.85</v>
+        <v>154734.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1552,16 +1893,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>195</v>
+        <v>967</v>
       </c>
       <c r="D20" t="n">
-        <v>66250.71000000001</v>
+        <v>795956.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1570,16 +1911,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>59</v>
+        <v>358</v>
       </c>
       <c r="D21" t="n">
-        <v>23191.48</v>
+        <v>173425.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1588,16 +1929,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>278</v>
+        <v>1006</v>
       </c>
       <c r="D22" t="n">
-        <v>91326.58</v>
+        <v>862217.26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1606,16 +1947,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>323</v>
       </c>
       <c r="D23" t="n">
-        <v>12780.28</v>
+        <v>135131.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1624,10 +1965,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>271</v>
+        <v>1341</v>
       </c>
       <c r="D24" t="n">
-        <v>88644.67999999999</v>
+        <v>1021074.28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>新用户</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>41</v>
+      </c>
+      <c r="D25" t="n">
+        <v>27005.46</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>老用户</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>574</v>
+      </c>
+      <c r="D26" t="n">
+        <v>490184.98</v>
       </c>
     </row>
   </sheetData>
@@ -1663,7 +2040,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1263</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="3">
@@ -1673,7 +2050,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>943</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="4">
@@ -1683,7 +2060,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7466</v>
+        <v>0.6558</v>
       </c>
     </row>
   </sheetData>
@@ -1734,16 +2111,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>185</v>
+        <v>942</v>
       </c>
       <c r="C2" t="n">
-        <v>25.06</v>
+        <v>12.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.32</v>
+        <v>11.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1636.67</v>
+        <v>6091.24</v>
       </c>
     </row>
     <row r="3">
@@ -1753,16 +2130,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>219</v>
+        <v>587</v>
       </c>
       <c r="C3" t="n">
-        <v>113.05</v>
+        <v>77.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.71</v>
+        <v>3.95</v>
       </c>
       <c r="E3" t="n">
-        <v>1353.88</v>
+        <v>2841.13</v>
       </c>
     </row>
     <row r="4">
@@ -1772,54 +2149,54 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>121</v>
+        <v>285</v>
       </c>
       <c r="C4" t="n">
-        <v>158.07</v>
+        <v>134.79</v>
       </c>
       <c r="D4" t="n">
-        <v>3.48</v>
+        <v>4.89</v>
       </c>
       <c r="E4" t="n">
-        <v>1181.59</v>
+        <v>1590.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>新客培育</t>
+          <t>一般用户</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>134</v>
+        <v>935</v>
       </c>
       <c r="C5" t="n">
-        <v>28.25</v>
+        <v>36.13</v>
       </c>
       <c r="D5" t="n">
-        <v>1.54</v>
+        <v>2.33</v>
       </c>
       <c r="E5" t="n">
-        <v>489.3</v>
+        <v>484.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>一般用户</t>
+          <t>新客培育</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>50.49</v>
+        <v>18.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.59</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="n">
-        <v>473.71</v>
+        <v>458.84</v>
       </c>
     </row>
     <row r="7">
@@ -1829,16 +2206,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>1279</v>
       </c>
       <c r="C7" t="n">
-        <v>207.07</v>
+        <v>208.24</v>
       </c>
       <c r="D7" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="E7" t="n">
-        <v>322.92</v>
+        <v>338.68</v>
       </c>
     </row>
   </sheetData>
@@ -1852,13 +2229,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1879,144 +2256,710 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>avg_order_value</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>order_per_user</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>自然搜索</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>287935.16</v>
+        <v>7285024.64</v>
       </c>
       <c r="C2" t="n">
-        <v>898</v>
+        <v>16646</v>
       </c>
       <c r="D2" t="n">
-        <v>657</v>
+        <v>3920</v>
       </c>
       <c r="E2" t="n">
-        <v>320.64</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.37</v>
+        <v>437.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>信息流广告</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>227362.02</v>
+        <v>285446.34</v>
       </c>
       <c r="C3" t="n">
-        <v>725</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n">
-        <v>570</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>313.6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.27</v>
+        <v>3036.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>直播间</t>
+          <t>EIRE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>226353.69</v>
+        <v>265262.46</v>
       </c>
       <c r="C4" t="n">
-        <v>669</v>
+        <v>260</v>
       </c>
       <c r="D4" t="n">
-        <v>537</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>338.35</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.25</v>
+        <v>1020.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>会员短信</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>155644.07</v>
+        <v>228678.4</v>
       </c>
       <c r="C5" t="n">
-        <v>518</v>
+        <v>457</v>
       </c>
       <c r="D5" t="n">
-        <v>439</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>300.47</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.18</v>
+        <v>500.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>社群团购</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>131794</v>
+        <v>208934.31</v>
       </c>
       <c r="C6" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D6" t="n">
-        <v>330</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>352.39</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.13</v>
+        <v>537.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>未知渠道</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19616.96</v>
+        <v>138453.81</v>
       </c>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2429.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>61558.56</v>
+      </c>
+      <c r="C8" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>683.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>56443.95</v>
+      </c>
+      <c r="C9" t="n">
         <v>51</v>
       </c>
-      <c r="E7" t="n">
-        <v>377.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.02</v>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1106.74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>41196.34</v>
+      </c>
+      <c r="C10" t="n">
+        <v>98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>420.37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>38367.83</v>
+      </c>
+      <c r="C11" t="n">
+        <v>36</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1065.77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>37416.37</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1969.28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>36165.44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1004.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>33375.84</v>
+      </c>
+      <c r="C14" t="n">
+        <v>57</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>585.54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>22546.08</v>
+      </c>
+      <c r="C15" t="n">
+        <v>41</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>549.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>21279.29</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3039.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Channel Islands</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>20440.54</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>786.17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18955.34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1053.07</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17483.24</v>
+      </c>
+      <c r="C19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>460.09</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13502.85</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>843.9299999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10198.68</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" t="n">
+        <v>599.92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7334.65</v>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>386.03</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7215.84</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1443.17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4760.52</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>952.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4310</v>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>615.71</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3666.38</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>611.0599999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3580.39</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>716.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2725.59</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>545.12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2660.77</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>332.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1902.28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>634.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1693.88</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1693.88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1661.06</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>415.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>European Community</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1300.25</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>325.06</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1143.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1143.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RSA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1002.31</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1002.31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>826.74</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>413.37</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>548.4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>274.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>145.92</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>145.92</v>
       </c>
     </row>
   </sheetData>
@@ -2030,13 +2973,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2057,159 +3000,1058 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>avg_order_value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sales_share</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>orders_share</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>aov_index</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>258553.42</v>
+        <v>7285024.64</v>
       </c>
       <c r="C2" t="n">
-        <v>811</v>
+        <v>16646</v>
       </c>
       <c r="D2" t="n">
-        <v>614</v>
+        <v>3920</v>
       </c>
       <c r="E2" t="n">
-        <v>318.81</v>
+        <v>437.64</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8982</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>234949.5</v>
+        <v>285446.34</v>
       </c>
       <c r="C3" t="n">
-        <v>716</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n">
-        <v>556</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>328.14</v>
+        <v>3036.66</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>EIRE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>167879.93</v>
+        <v>265262.46</v>
       </c>
       <c r="C4" t="n">
-        <v>548</v>
+        <v>260</v>
       </c>
       <c r="D4" t="n">
-        <v>447</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>306.35</v>
+        <v>1020.24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>129266.03</v>
+        <v>228678.4</v>
       </c>
       <c r="C5" t="n">
-        <v>412</v>
+        <v>457</v>
       </c>
       <c r="D5" t="n">
-        <v>359</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>313.75</v>
+        <v>500.39</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115959.05</v>
+        <v>208934.31</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>389</v>
       </c>
       <c r="D6" t="n">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>381.44</v>
+        <v>537.11</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>东北</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70468.19</v>
+        <v>138453.81</v>
       </c>
       <c r="C7" t="n">
-        <v>223</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>210</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>316</v>
+        <v>2429.01</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61287.78</v>
+        <v>61558.56</v>
       </c>
       <c r="C8" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>322.57</v>
+        <v>683.98</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未知地区</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10342</v>
+        <v>56443.95</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>323.19</v>
+        <v>1106.74</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>41196.34</v>
+      </c>
+      <c r="C10" t="n">
+        <v>98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>420.37</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>38367.83</v>
+      </c>
+      <c r="C11" t="n">
+        <v>36</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1065.77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>37416.37</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1969.28</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>36165.44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1004.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>33375.84</v>
+      </c>
+      <c r="C14" t="n">
+        <v>57</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>585.54</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>22546.08</v>
+      </c>
+      <c r="C15" t="n">
+        <v>41</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>549.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>21279.29</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3039.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Channel Islands</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>20440.54</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>786.17</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18955.34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1053.07</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>17483.24</v>
+      </c>
+      <c r="C19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>460.09</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13502.85</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>843.9299999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10198.68</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" t="n">
+        <v>599.92</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7334.65</v>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7215.84</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1443.17</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4760.52</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>952.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4310</v>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>615.71</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3666.38</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>611.0599999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3580.39</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>716.08</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2725.59</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>545.12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unspecified</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2660.77</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1902.28</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>634.09</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1693.88</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1693.88</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1661.06</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>415.26</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>European Community</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1300.25</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1143.6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1143.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RSA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1002.31</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1002.31</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>826.74</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>413.37</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>548.4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>145.92</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>145.92</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -2223,7 +4065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2246,195 +4088,375 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3946</v>
+        <v>0.897</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1892</v>
+        <v>0.0297</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>东北</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1297</v>
+        <v>0.0287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1189</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1135</v>
+        <v>0.0064</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0324</v>
+        <v>0.0042</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0216</v>
+        <v>0.0032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>地区</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>会员短信</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3081</v>
+        <v>0.0032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>信息流广告</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2649</v>
+        <v>0.0032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>自然搜索</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2216</v>
+        <v>0.0021</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>直播间</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1676</v>
+        <v>0.0021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>社群团购</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0324</v>
+        <v>0.0021</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>国家/地区</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>未知渠道</t>
+          <t>EIRE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0054</v>
+        <v>0.0021</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>渠道</t>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Channel Islands</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>国家/地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>礼品套装</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>其他商品</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.3684</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>家居装饰</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>厨房餐具</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>收纳用品</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>节日季节</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
         </is>
       </c>
     </row>

--- a/reports/powerbi/powerbi_dashboard_dataset.xlsx
+++ b/reports/powerbi/powerbi_dashboard_dataset.xlsx
@@ -13,10 +13,10 @@
     <sheet name="user_type" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="repeat_rate" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="rfm_summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="country_metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="country_gap" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="high_value_profile" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="channel_limitation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="channel_metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="region_metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="segment_metrics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="high_value_profile" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="data_quality" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
@@ -456,248 +456,248 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>570422.73</v>
+        <v>171245.21</v>
       </c>
       <c r="C2" t="n">
-        <v>1400</v>
+        <v>338</v>
       </c>
       <c r="D2" t="n">
-        <v>885</v>
+        <v>304</v>
       </c>
       <c r="E2" t="n">
-        <v>407.44</v>
+        <v>506.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>568101.3100000001</v>
+        <v>459730.04</v>
       </c>
       <c r="C3" t="n">
-        <v>987</v>
+        <v>831</v>
       </c>
       <c r="D3" t="n">
-        <v>741</v>
+        <v>660</v>
       </c>
       <c r="E3" t="n">
-        <v>575.58</v>
+        <v>553.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>446084.92</v>
+        <v>445860.59</v>
       </c>
       <c r="C4" t="n">
-        <v>997</v>
+        <v>820</v>
       </c>
       <c r="D4" t="n">
-        <v>758</v>
+        <v>625</v>
       </c>
       <c r="E4" t="n">
-        <v>447.43</v>
+        <v>543.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>594081.76</v>
+        <v>450430.87</v>
       </c>
       <c r="C5" t="n">
-        <v>1321</v>
+        <v>813</v>
       </c>
       <c r="D5" t="n">
-        <v>974</v>
+        <v>654</v>
       </c>
       <c r="E5" t="n">
-        <v>449.72</v>
+        <v>554.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>468374.33</v>
+        <v>408858.89</v>
       </c>
       <c r="C6" t="n">
-        <v>1149</v>
+        <v>829</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>647</v>
       </c>
       <c r="E6" t="n">
-        <v>407.64</v>
+        <v>493.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>677355.15</v>
+        <v>414212.86</v>
       </c>
       <c r="C7" t="n">
-        <v>1555</v>
+        <v>776</v>
       </c>
       <c r="D7" t="n">
-        <v>1056</v>
+        <v>637</v>
       </c>
       <c r="E7" t="n">
-        <v>435.6</v>
+        <v>533.78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>660046.05</v>
+        <v>465007.54</v>
       </c>
       <c r="C8" t="n">
-        <v>1393</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>991</v>
+        <v>677</v>
       </c>
       <c r="E8" t="n">
-        <v>473.83</v>
+        <v>526.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>598962.9</v>
+        <v>441851.41</v>
       </c>
       <c r="C9" t="n">
-        <v>1331</v>
+        <v>836</v>
       </c>
       <c r="D9" t="n">
-        <v>949</v>
+        <v>665</v>
       </c>
       <c r="E9" t="n">
-        <v>450.01</v>
+        <v>528.53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>644051.04</v>
+        <v>446431.63</v>
       </c>
       <c r="C10" t="n">
-        <v>1280</v>
+        <v>825</v>
       </c>
       <c r="D10" t="n">
-        <v>935</v>
+        <v>640</v>
       </c>
       <c r="E10" t="n">
-        <v>503.16</v>
+        <v>541.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>950690.2</v>
+        <v>470023.44</v>
       </c>
       <c r="C11" t="n">
-        <v>1755</v>
+        <v>887</v>
       </c>
       <c r="D11" t="n">
-        <v>1266</v>
+        <v>696</v>
       </c>
       <c r="E11" t="n">
-        <v>541.7</v>
+        <v>529.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1035642.45</v>
+        <v>406470.81</v>
       </c>
       <c r="C12" t="n">
-        <v>1929</v>
+        <v>755</v>
       </c>
       <c r="D12" t="n">
-        <v>1364</v>
+        <v>607</v>
       </c>
       <c r="E12" t="n">
-        <v>536.88</v>
+        <v>538.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1156205.61</v>
+        <v>476589.29</v>
       </c>
       <c r="C13" t="n">
-        <v>2657</v>
+        <v>870</v>
       </c>
       <c r="D13" t="n">
-        <v>1664</v>
+        <v>681</v>
       </c>
       <c r="E13" t="n">
-        <v>435.15</v>
+        <v>547.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>517190.44</v>
+        <v>278220.28</v>
       </c>
       <c r="C14" t="n">
-        <v>778</v>
+        <v>536</v>
       </c>
       <c r="D14" t="n">
-        <v>615</v>
+        <v>457</v>
       </c>
       <c r="E14" t="n">
-        <v>664.77</v>
+        <v>519.0700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -711,30 +711,908 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>dimension_value</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dimension</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>渠道分析限制</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>UCI Online Retail 原始数据不包含广告渠道、流量来源或转化漏斗字段，因此本项目不伪造渠道分析，改用真实国家/地区字段做区域表现分析。</t>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>付费搜索</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>社交媒体</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>自然流量</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>邮件营销</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>渠道</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>图书</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>家居</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.2182</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>服饰</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>玩具</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>美妆</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>偏好品类</t>
         </is>
       </c>
     </row>
@@ -749,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,70 +1643,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>license</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>raw_rows</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cancel_rows</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>missing_customer_rows</t>
+          <t>missing_required_rows</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>negative_or_zero_quantity_rows</t>
+          <t>rows_after_required_drop</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>required_rows_removed</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>duplicate_orders_removed</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>non_positive_price_rows</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>rows_after_required_drop</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>required_rows_removed</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>duplicate_rows_removed</t>
+          <t>non_positive_quantity_rows</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>clean_rows_before_business_filter</t>
+          <t>clean_rows</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>valid_purchase_rows</t>
+          <t>valid_orders</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>valid_orders</t>
+          <t>valid_users</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>valid_users</t>
+          <t>date_min</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>date_min</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>date_max</t>
         </is>
@@ -837,58 +1710,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UCI Online Retail</t>
+          <t>Hugging Face millat/e-commerce-orders</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://archive.ics.uci.edu/dataset/352/online+retail</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>541909</v>
+          <t>https://huggingface.co/datasets/millat/e-commerce-orders</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>9288</v>
+        <v>10000</v>
       </c>
       <c r="E2" t="n">
-        <v>135080</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>10624</v>
+        <v>10000</v>
       </c>
       <c r="G2" t="n">
-        <v>2517</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>406829</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>135080</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5225</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>401604</v>
+        <v>10000</v>
       </c>
       <c r="L2" t="n">
-        <v>392692</v>
+        <v>10000</v>
       </c>
       <c r="M2" t="n">
-        <v>18532</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4338</v>
+        <v>2713</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024-04-20 14:59:58.897063</t>
+        </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2010-12-01 08:26:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2011-12-09 12:50:00</t>
+          <t>2025-04-19 14:59:58.897063</t>
         </is>
       </c>
     </row>
@@ -903,7 +1775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,20 +1786,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>category_cn</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sales_share</t>
         </is>
@@ -936,153 +1813,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>其他商品</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2614170.33</v>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>家居</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>15557</v>
+        <v>921394.85</v>
       </c>
       <c r="D2" t="n">
-        <v>4049</v>
+        <v>1713</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2941</v>
+        <v>1159</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1727</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>礼品套装</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2356228.6</v>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>电子产品</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>14586</v>
+        <v>910153.11</v>
       </c>
       <c r="D3" t="n">
-        <v>3898</v>
+        <v>1694</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2651</v>
+        <v>1142</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>家居装饰</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1786295.2</v>
+          <t>Beauty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>美妆</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>13892</v>
+        <v>888823.1899999999</v>
       </c>
       <c r="D4" t="n">
-        <v>3846</v>
+        <v>1682</v>
       </c>
       <c r="E4" t="n">
-        <v>0.201</v>
+        <v>1145</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>厨房餐具</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1315517.29</v>
+          <t>Toys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>玩具</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>12455</v>
+        <v>888447.7</v>
       </c>
       <c r="D5" t="n">
-        <v>3588</v>
+        <v>1666</v>
       </c>
       <c r="E5" t="n">
-        <v>0.148</v>
+        <v>1130</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>收纳用品</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>408962.18</v>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>服饰</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>5768</v>
+        <v>863629.45</v>
       </c>
       <c r="D6" t="n">
-        <v>2161</v>
+        <v>1620</v>
       </c>
       <c r="E6" t="n">
-        <v>0.046</v>
+        <v>1113</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1619</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>节日季节</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>255607.74</v>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>图书</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>5599</v>
+        <v>862484.5600000001</v>
       </c>
       <c r="D7" t="n">
-        <v>2396</v>
+        <v>1625</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0288</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>儿童用品</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>120906.02</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3598</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1731</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0136</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>服饰配件</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>29521.53</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D9" t="n">
-        <v>773</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0033</v>
+        <v>1101</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1617</v>
       </c>
     </row>
   </sheetData>
@@ -1096,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1107,418 +1976,468 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>category_cn</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>product_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>orders</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>995</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PAPER CRAFT , LITTLE BIRDIE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>其他商品</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7048.14</v>
       </c>
       <c r="D2" t="n">
-        <v>168469.6</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>80995</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>363.31</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>商品ID-995</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>585</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REGENCY CAKESTAND 3 TIER</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>厨房餐具</t>
-        </is>
+          <t>美妆</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6749.61</v>
       </c>
       <c r="D3" t="n">
-        <v>142264.75</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>12374</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1703</v>
+        <v>367.4</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>商品ID-585</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>85123A</t>
+          <t>955</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WHITE HANGING HEART T-LIGHT HOLDER</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>家居装饰</t>
-        </is>
+          <t>美妆</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6370.36</v>
       </c>
       <c r="D4" t="n">
-        <v>100392.1</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>36706</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>1971</v>
+        <v>376.49</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>商品ID-955</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>85099B</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JUMBO BAG RED RETROSPOT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>礼品套装</t>
-        </is>
+          <t>服饰</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5641.68</v>
       </c>
       <c r="D5" t="n">
-        <v>85040.53999999999</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>46078</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1600</v>
+        <v>466.47</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>商品ID-43</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>812</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEDIUM CERAMIC TOP STORAGE JAR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>收纳用品</t>
-        </is>
+          <t>家居</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5618.82</v>
       </c>
       <c r="D6" t="n">
-        <v>81416.73</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>77916</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>195</v>
+        <v>333.74</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>商品ID-812</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>957</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POSTAGE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>礼品套装</t>
-        </is>
+          <t>玩具</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5545.54</v>
       </c>
       <c r="D7" t="n">
-        <v>77803.96000000001</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>3120</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>1099</v>
+        <v>329.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>商品ID-957</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>47566</t>
+          <t>832</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PARTY BUNTING</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>节日季节</t>
-        </is>
+          <t>美妆</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5450.8</v>
       </c>
       <c r="D8" t="n">
-        <v>68785.23</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>15279</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>1379</v>
+        <v>354.48</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>商品ID-832</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>84879</t>
+          <t>827</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASSORTED COLOUR BIRD ORNAMENT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>其他商品</t>
-        </is>
+          <t>美妆</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5450.64</v>
       </c>
       <c r="D9" t="n">
-        <v>56413.03</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>35263</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>1375</v>
+        <v>296.36</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>商品ID-827</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>其他商品</t>
-        </is>
+          <t>家居</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5402.78</v>
       </c>
       <c r="D10" t="n">
-        <v>53419.93</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>6933</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>253</v>
+        <v>314.21</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>商品ID-102</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>398</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RABBIT NIGHT LIGHT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>家居装饰</t>
-        </is>
+          <t>家居</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5395.48</v>
       </c>
       <c r="D11" t="n">
-        <v>51251.24</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>27153</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>801</v>
+        <v>235.56</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>商品ID-398</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>79321</t>
+          <t>471</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHILLI LIGHTS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>家居装饰</t>
-        </is>
+          <t>图书</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5365.76</v>
       </c>
       <c r="D12" t="n">
-        <v>46265.11</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>9646</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>519</v>
+        <v>366.02</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>商品ID-471</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>700</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAPER CHAIN KIT 50'S CHRISTMAS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>节日季节</t>
-        </is>
+          <t>美妆</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5338.71</v>
       </c>
       <c r="D13" t="n">
-        <v>42584.13</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>15591</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>980</v>
+        <v>387.22</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>商品ID-700</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>477</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PICNIC BASKET WICKER 60 PIECES</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>收纳用品</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5175.98</v>
       </c>
       <c r="D14" t="n">
-        <v>39619.5</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>332.66</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>商品ID-477</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>642</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BLACK RECORD COVER FRAME</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>家居装饰</t>
-        </is>
+          <t>电子产品</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5166.67</v>
       </c>
       <c r="D15" t="n">
-        <v>39045.8</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>11401</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>313</v>
+        <v>289.88</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>商品ID-642</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>551</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JUMBO BAG PINK POLKADOT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>礼品套装</t>
-        </is>
+          <t>图书</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5065.53</v>
       </c>
       <c r="D16" t="n">
-        <v>37254.36</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>20148</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>871</v>
+        <v>236.63</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>商品ID-551</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1560,7 +2479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1569,16 +2488,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>885</v>
+        <v>304</v>
       </c>
       <c r="D2" t="n">
-        <v>570422.73</v>
+        <v>171245.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1587,16 +2506,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>417</v>
+        <v>576</v>
       </c>
       <c r="D3" t="n">
-        <v>292366.84</v>
+        <v>379491.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1605,16 +2524,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>275734.47</v>
+        <v>80238.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1623,16 +2542,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>157700.59</v>
+        <v>260363.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1641,16 +2560,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="D6" t="n">
-        <v>288384.33</v>
+        <v>185496.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1659,16 +2578,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>452</v>
+        <v>313</v>
       </c>
       <c r="D7" t="n">
-        <v>199619.67</v>
+        <v>186753.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1677,16 +2596,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>522</v>
+        <v>341</v>
       </c>
       <c r="D8" t="n">
-        <v>394462.09</v>
+        <v>263677.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1695,16 +2614,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>121809.05</v>
+        <v>152057.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1713,16 +2632,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>556</v>
+        <v>388</v>
       </c>
       <c r="D10" t="n">
-        <v>346565.28</v>
+        <v>256801.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1731,16 +2650,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>123739.3</v>
+        <v>130208.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1749,16 +2668,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>772</v>
+        <v>435</v>
       </c>
       <c r="D12" t="n">
-        <v>553615.85</v>
+        <v>284003.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1767,16 +2686,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="D13" t="n">
-        <v>135414.8</v>
+        <v>122834.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1785,16 +2704,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>749</v>
+        <v>495</v>
       </c>
       <c r="D14" t="n">
-        <v>524631.25</v>
+        <v>342172.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1803,16 +2722,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="D15" t="n">
-        <v>73860.39999999999</v>
+        <v>72118.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1821,16 +2740,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>761</v>
+        <v>523</v>
       </c>
       <c r="D16" t="n">
-        <v>525102.5</v>
+        <v>369733.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1839,16 +2758,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="D17" t="n">
-        <v>79601.14</v>
+        <v>61722.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1857,16 +2776,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>766</v>
+        <v>542</v>
       </c>
       <c r="D18" t="n">
-        <v>564449.9</v>
+        <v>384709.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,16 +2794,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>299</v>
+        <v>89</v>
       </c>
       <c r="D19" t="n">
-        <v>154734.09</v>
+        <v>54155.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1893,16 +2812,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>967</v>
+        <v>607</v>
       </c>
       <c r="D20" t="n">
-        <v>795956.11</v>
+        <v>415868.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1911,16 +2830,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>358</v>
+        <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>173425.19</v>
+        <v>40015.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1929,16 +2848,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1006</v>
+        <v>539</v>
       </c>
       <c r="D22" t="n">
-        <v>862217.26</v>
+        <v>366454.83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1947,16 +2866,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>323</v>
+        <v>56</v>
       </c>
       <c r="D23" t="n">
-        <v>135131.33</v>
+        <v>32304.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1965,16 +2884,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1341</v>
+        <v>625</v>
       </c>
       <c r="D24" t="n">
-        <v>1021074.28</v>
+        <v>444284.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1983,16 +2902,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>27005.46</v>
+        <v>13532.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2001,10 +2920,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>574</v>
+        <v>433</v>
       </c>
       <c r="D26" t="n">
-        <v>490184.98</v>
+        <v>264687.9</v>
       </c>
     </row>
   </sheetData>
@@ -2040,7 +2959,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4338</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="3">
@@ -2050,7 +2969,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2845</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="4">
@@ -2060,7 +2979,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6558</v>
+        <v>0.7914</v>
       </c>
     </row>
   </sheetData>
@@ -2111,16 +3030,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>942</v>
+        <v>527</v>
       </c>
       <c r="C2" t="n">
-        <v>12.5</v>
+        <v>23.86</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6091.24</v>
+        <v>4577.4</v>
       </c>
     </row>
     <row r="3">
@@ -2130,16 +3049,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>587</v>
+        <v>405</v>
       </c>
       <c r="C3" t="n">
-        <v>77.5</v>
+        <v>99.75</v>
       </c>
       <c r="D3" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="E3" t="n">
-        <v>2841.13</v>
+        <v>2769.74</v>
       </c>
     </row>
     <row r="4">
@@ -2149,16 +3068,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="C4" t="n">
-        <v>134.79</v>
+        <v>157.31</v>
       </c>
       <c r="D4" t="n">
-        <v>4.89</v>
+        <v>4.48</v>
       </c>
       <c r="E4" t="n">
-        <v>1590.72</v>
+        <v>2406.03</v>
       </c>
     </row>
     <row r="5">
@@ -2168,16 +3087,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>935</v>
+        <v>591</v>
       </c>
       <c r="C5" t="n">
-        <v>36.13</v>
+        <v>55.25</v>
       </c>
       <c r="D5" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="E5" t="n">
-        <v>484.22</v>
+        <v>1000.11</v>
       </c>
     </row>
     <row r="6">
@@ -2187,16 +3106,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>18.1</v>
+        <v>28.49</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="E6" t="n">
-        <v>458.84</v>
+        <v>872.21</v>
       </c>
     </row>
     <row r="7">
@@ -2206,16 +3125,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1279</v>
+        <v>764</v>
       </c>
       <c r="C7" t="n">
-        <v>208.24</v>
+        <v>210.87</v>
       </c>
       <c r="D7" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="E7" t="n">
-        <v>338.68</v>
+        <v>693.6900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2229,737 +3148,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>channel_cn</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>avg_order_value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>order_per_user</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sales_share</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>7285024.64</v>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>社交媒体</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>16646</v>
+        <v>1358397.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3920</v>
+        <v>2566</v>
       </c>
       <c r="E2" t="n">
-        <v>437.64</v>
+        <v>1531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>529.38</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2546</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>285446.34</v>
+          <t>Paid Search</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>付费搜索</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>1357065.26</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>2525</v>
       </c>
       <c r="E3" t="n">
-        <v>3036.66</v>
+        <v>1514</v>
+      </c>
+      <c r="F3" t="n">
+        <v>537.45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2544</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EIRE</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>265262.46</v>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>邮件营销</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>260</v>
+        <v>1349734.63</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2474</v>
       </c>
       <c r="E4" t="n">
-        <v>1020.24</v>
+        <v>1477</v>
+      </c>
+      <c r="F4" t="n">
+        <v>545.5700000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.253</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>228678.4</v>
+          <t>Organic</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>自然流量</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>457</v>
+        <v>1269735.67</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>2435</v>
       </c>
       <c r="E5" t="n">
-        <v>500.39</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>208934.31</v>
-      </c>
-      <c r="C6" t="n">
-        <v>389</v>
-      </c>
-      <c r="D6" t="n">
-        <v>87</v>
-      </c>
-      <c r="E6" t="n">
-        <v>537.11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>138453.81</v>
-      </c>
-      <c r="C7" t="n">
-        <v>57</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2429.01</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>61558.56</v>
-      </c>
-      <c r="C8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" t="n">
-        <v>30</v>
-      </c>
-      <c r="E8" t="n">
-        <v>683.98</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>56443.95</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1106.74</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>41196.34</v>
-      </c>
-      <c r="C10" t="n">
-        <v>98</v>
-      </c>
-      <c r="D10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E10" t="n">
-        <v>420.37</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>38367.83</v>
-      </c>
-      <c r="C11" t="n">
-        <v>36</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1065.77</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>37416.37</v>
-      </c>
-      <c r="C12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1969.28</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>36165.44</v>
-      </c>
-      <c r="C13" t="n">
-        <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1004.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>33375.84</v>
-      </c>
-      <c r="C14" t="n">
-        <v>57</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E14" t="n">
-        <v>585.54</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>22546.08</v>
-      </c>
-      <c r="C15" t="n">
-        <v>41</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12</v>
-      </c>
-      <c r="E15" t="n">
-        <v>549.9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>21279.29</v>
-      </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3039.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Channel Islands</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>20440.54</v>
-      </c>
-      <c r="C17" t="n">
-        <v>26</v>
-      </c>
-      <c r="D17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>786.17</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>18955.34</v>
-      </c>
-      <c r="C18" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1053.07</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>17483.24</v>
-      </c>
-      <c r="C19" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" t="n">
-        <v>14</v>
-      </c>
-      <c r="E19" t="n">
-        <v>460.09</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Cyprus</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>13502.85</v>
-      </c>
-      <c r="C20" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" t="n">
-        <v>8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>843.9299999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>10198.68</v>
-      </c>
-      <c r="C21" t="n">
-        <v>17</v>
-      </c>
-      <c r="D21" t="n">
-        <v>11</v>
-      </c>
-      <c r="E21" t="n">
-        <v>599.92</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>7334.65</v>
-      </c>
-      <c r="C22" t="n">
-        <v>19</v>
-      </c>
-      <c r="D22" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" t="n">
-        <v>386.03</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>7215.84</v>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1443.17</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4760.52</v>
-      </c>
-      <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>952.1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4310</v>
-      </c>
-      <c r="C25" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>615.71</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3666.38</v>
-      </c>
-      <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>611.0599999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3580.39</v>
-      </c>
-      <c r="C27" t="n">
-        <v>5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>716.08</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2725.59</v>
-      </c>
-      <c r="C28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>545.12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unspecified</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2660.77</v>
-      </c>
-      <c r="C29" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="n">
-        <v>332.6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1902.28</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>634.09</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1693.88</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1693.88</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1661.06</v>
-      </c>
-      <c r="C32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>415.26</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>European Community</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1300.25</v>
-      </c>
-      <c r="C33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>325.06</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1143.6</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1143.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RSA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1002.31</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1002.31</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>826.74</v>
-      </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>413.37</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Bahrain</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>548.4</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>274.2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>145.92</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>145.92</v>
+        <v>1443</v>
+      </c>
+      <c r="F5" t="n">
+        <v>521.45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.238</v>
       </c>
     </row>
   </sheetData>
@@ -2973,13 +3324,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3005,1053 +3356,1107 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>sales_share</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>orders_share</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>aov_index</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7285024.64</v>
+        <v>131175.29</v>
       </c>
       <c r="C2" t="n">
-        <v>16646</v>
+        <v>223</v>
       </c>
       <c r="D2" t="n">
-        <v>3920</v>
+        <v>201</v>
       </c>
       <c r="E2" t="n">
-        <v>437.64</v>
+        <v>588.23</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8197</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.8982</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.91</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>285446.34</v>
+        <v>125751.38</v>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="E3" t="n">
-        <v>3036.66</v>
+        <v>587.62</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0321</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6.33</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EIRE</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>265262.46</v>
+        <v>125267.35</v>
       </c>
       <c r="C4" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>207</v>
       </c>
       <c r="E4" t="n">
-        <v>1020.24</v>
+        <v>582.64</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0298</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.13</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228678.4</v>
+        <v>125211.27</v>
       </c>
       <c r="C5" t="n">
-        <v>457</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="E5" t="n">
-        <v>500.39</v>
+        <v>569.14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0257</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0247</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.04</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>208934.31</v>
+        <v>124163.32</v>
       </c>
       <c r="C6" t="n">
-        <v>389</v>
+        <v>221</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="E6" t="n">
-        <v>537.11</v>
+        <v>561.8200000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.12</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>138453.81</v>
+        <v>119567.67</v>
       </c>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>211</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>192</v>
       </c>
       <c r="E7" t="n">
-        <v>2429.01</v>
+        <v>566.67</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5.07</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61558.56</v>
+        <v>115697.78</v>
       </c>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>217</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>208</v>
       </c>
       <c r="E8" t="n">
-        <v>683.98</v>
+        <v>533.17</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0049</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.43</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56443.95</v>
+        <v>114856.96</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>221</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="E9" t="n">
-        <v>1106.74</v>
+        <v>519.71</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.31</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41196.34</v>
+        <v>113970.06</v>
       </c>
       <c r="C10" t="n">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>202</v>
       </c>
       <c r="E10" t="n">
-        <v>420.37</v>
+        <v>527.64</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.88</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38367.83</v>
+        <v>113539.62</v>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>186</v>
       </c>
       <c r="E11" t="n">
-        <v>1065.77</v>
+        <v>579.28</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.22</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37416.37</v>
+        <v>112917.46</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="E12" t="n">
-        <v>1969.28</v>
+        <v>597.45</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.11</v>
+        <v>0.0212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36165.44</v>
+        <v>112687.69</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>197</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="E13" t="n">
-        <v>1004.6</v>
+        <v>572.02</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.09</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33375.84</v>
+        <v>112649.02</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>210</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="E14" t="n">
-        <v>585.54</v>
+        <v>536.42</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0038</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.22</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22546.08</v>
+        <v>110953.55</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>217</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="E15" t="n">
-        <v>549.9</v>
+        <v>511.31</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.15</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21279.29</v>
+        <v>110182.47</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="E16" t="n">
-        <v>3039.9</v>
+        <v>573.87</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6.34</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Channel Islands</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20440.54</v>
+        <v>109603.08</v>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>198</v>
       </c>
       <c r="E17" t="n">
-        <v>786.17</v>
+        <v>521.92</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.64</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Maine</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18955.34</v>
+        <v>109581.38</v>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>193</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="E18" t="n">
-        <v>1053.07</v>
+        <v>567.78</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.2</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17483.24</v>
+        <v>109156.69</v>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="E19" t="n">
-        <v>460.09</v>
+        <v>562.66</v>
       </c>
       <c r="F19" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.96</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13502.85</v>
+        <v>109094.41</v>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="E20" t="n">
-        <v>843.9299999999999</v>
+        <v>559.46</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.76</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10198.68</v>
+        <v>108660.54</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>185</v>
       </c>
       <c r="E21" t="n">
-        <v>599.92</v>
+        <v>546.03</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.25</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7334.65</v>
+        <v>108610.54</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>198</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="E22" t="n">
-        <v>386.03</v>
+        <v>548.54</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.8</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7215.84</v>
+        <v>108306.84</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>211</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>195</v>
       </c>
       <c r="E23" t="n">
-        <v>1443.17</v>
+        <v>513.3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.01</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4760.52</v>
+        <v>108123.28</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>212</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>197</v>
       </c>
       <c r="E24" t="n">
-        <v>952.1</v>
+        <v>510.02</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.99</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4310</v>
+        <v>107905.14</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>212</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E25" t="n">
-        <v>615.71</v>
+        <v>508.99</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.28</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3666.38</v>
+        <v>107811.28</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>214</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>192</v>
       </c>
       <c r="E26" t="n">
-        <v>611.0599999999999</v>
+        <v>503.79</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.27</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3580.39</v>
+        <v>107264.64</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>192</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>175</v>
       </c>
       <c r="E27" t="n">
-        <v>716.08</v>
+        <v>558.67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.49</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2725.59</v>
+        <v>107042.18</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>195</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="E28" t="n">
-        <v>545.12</v>
+        <v>548.9299999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.14</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2660.77</v>
+        <v>105071.96</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>190</v>
       </c>
       <c r="E29" t="n">
-        <v>332.6</v>
+        <v>522.75</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1902.28</v>
+        <v>105071.44</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>195</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="E30" t="n">
-        <v>634.09</v>
+        <v>538.83</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.32</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1693.88</v>
+        <v>104517.2</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>190</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="E31" t="n">
-        <v>1693.88</v>
+        <v>550.09</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.53</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1661.06</v>
+        <v>104423.77</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>208</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="E32" t="n">
-        <v>415.26</v>
+        <v>502.04</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.87</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>European Community</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1300.25</v>
+        <v>104343.03</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="E33" t="n">
-        <v>325.06</v>
+        <v>511.49</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.68</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1143.6</v>
+        <v>102794.42</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="E34" t="n">
-        <v>1143.6</v>
+        <v>508.88</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.38</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RSA</t>
+          <t>Alaska</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1002.31</v>
+        <v>101868.51</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="E35" t="n">
-        <v>1002.31</v>
+        <v>517.1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2.09</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>826.74</v>
+        <v>101653.92</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>188</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="E36" t="n">
-        <v>413.37</v>
+        <v>540.71</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.86</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Vermont</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>548.4</v>
+        <v>101456.23</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="E37" t="n">
-        <v>274.2</v>
+        <v>531.1799999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.57</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>145.92</v>
+        <v>101199.61</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="E38" t="n">
-        <v>145.92</v>
+        <v>508.54</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.3</v>
+        <v>0.019</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>100171.79</v>
+      </c>
+      <c r="C39" t="n">
+        <v>180</v>
+      </c>
+      <c r="D39" t="n">
+        <v>165</v>
+      </c>
+      <c r="E39" t="n">
+        <v>556.51</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0188</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>99407.31</v>
+      </c>
+      <c r="C40" t="n">
+        <v>211</v>
+      </c>
+      <c r="D40" t="n">
+        <v>196</v>
+      </c>
+      <c r="E40" t="n">
+        <v>471.12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0186</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>98216.38</v>
+      </c>
+      <c r="C41" t="n">
+        <v>179</v>
+      </c>
+      <c r="D41" t="n">
+        <v>167</v>
+      </c>
+      <c r="E41" t="n">
+        <v>548.6900000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0184</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>98150.64999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>186</v>
+      </c>
+      <c r="D42" t="n">
+        <v>172</v>
+      </c>
+      <c r="E42" t="n">
+        <v>527.6900000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>98131.10000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>187</v>
+      </c>
+      <c r="D43" t="n">
+        <v>173</v>
+      </c>
+      <c r="E43" t="n">
+        <v>524.77</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0184</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>96809.35000000001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>193</v>
+      </c>
+      <c r="D44" t="n">
+        <v>178</v>
+      </c>
+      <c r="E44" t="n">
+        <v>501.6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0181</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>96624.57000000001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>174</v>
+      </c>
+      <c r="D45" t="n">
+        <v>166</v>
+      </c>
+      <c r="E45" t="n">
+        <v>555.3099999999999</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0181</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>96037.77</v>
+      </c>
+      <c r="C46" t="n">
+        <v>218</v>
+      </c>
+      <c r="D46" t="n">
+        <v>192</v>
+      </c>
+      <c r="E46" t="n">
+        <v>440.54</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>94729.96000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>202</v>
+      </c>
+      <c r="D47" t="n">
+        <v>189</v>
+      </c>
+      <c r="E47" t="n">
+        <v>468.96</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0178</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>92284.78</v>
+      </c>
+      <c r="C48" t="n">
+        <v>187</v>
+      </c>
+      <c r="D48" t="n">
+        <v>172</v>
+      </c>
+      <c r="E48" t="n">
+        <v>493.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0173</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>92259.85000000001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>188</v>
+      </c>
+      <c r="D49" t="n">
+        <v>175</v>
+      </c>
+      <c r="E49" t="n">
+        <v>490.74</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.0173</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>89146.36</v>
+      </c>
+      <c r="C50" t="n">
+        <v>163</v>
+      </c>
+      <c r="D50" t="n">
+        <v>150</v>
+      </c>
+      <c r="E50" t="n">
+        <v>546.91</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.0167</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>80812.00999999999</v>
+      </c>
+      <c r="C51" t="n">
+        <v>173</v>
+      </c>
+      <c r="D51" t="n">
+        <v>161</v>
+      </c>
+      <c r="E51" t="n">
+        <v>467.12</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0151</v>
       </c>
     </row>
   </sheetData>
@@ -4065,399 +4470,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>dimension_value</t>
+          <t>customer_segment</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>customer_segment_cn</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>dimension</t>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_shipping_days</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_order_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2722687.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>614</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G2" t="n">
+        <v>528.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.0297</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
+          <t>Returning</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>回访客</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2316406.64</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4285</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1533</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="G3" t="n">
+        <v>540.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>EIRE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Channel Islands</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>国家/地区</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>礼品套装</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.4055</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>偏好品类</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>其他商品</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.3684</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>偏好品类</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>家居装饰</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.1571</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>偏好品类</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>厨房餐具</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>偏好品类</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>收纳用品</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>偏好品类</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>节日季节</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>偏好品类</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新客</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>295839.12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>566</v>
+      </c>
+      <c r="E4" t="n">
+        <v>566</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="G4" t="n">
+        <v>522.6799999999999</v>
       </c>
     </row>
   </sheetData>
